--- a/artfynd/A 4714-2026 artfynd.xlsx
+++ b/artfynd/A 4714-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>82452884</v>
+        <v>1918215</v>
       </c>
       <c r="B2" t="n">
-        <v>57484</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,56 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Söderön, Upl</t>
+          <t>(12J6a09), Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698374.0148044191</v>
+        <v>698533</v>
       </c>
       <c r="R2" t="n">
-        <v>6684119.178954441</v>
+        <v>6684187</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>21:30</t>
+          <t>2000-04-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>04:00</t>
+          <t>2000-04-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>120960091 / ART LEUC / Enstaka-sparsam (1)  / OBJ.AREA:3,9 ha</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,27 +765,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marielle Cambronero</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>82452882</v>
       </c>
       <c r="B3" t="n">
-        <v>57484</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -865,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698459.9811584731</v>
+        <v>698460</v>
       </c>
       <c r="R3" t="n">
-        <v>6684132.809774115</v>
+        <v>6684133</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -934,6 +904,344 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>82452884</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Söderön, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>698374</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6684119</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2019-07-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Marielle Cambronero</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2211946</v>
+      </c>
+      <c r="B5" t="n">
+        <v>111390</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>(12J6a09), Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>698533</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6684187</v>
+      </c>
+      <c r="S5" t="n">
+        <v>100</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2000-04-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2000-04-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>120960091 / SANI EUR / Enstaka-sparsam (1)  / OBJ.AREA:3,9 ha</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4342009</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>(12J6a09), Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>698533</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6684187</v>
+      </c>
+      <c r="S6" t="n">
+        <v>100</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2000-04-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2000-04-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>120960091 / LIST COR / Enstaka-sparsam (1)  / OBJ.AREA:3,9 ha</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4714-2026 artfynd.xlsx
+++ b/artfynd/A 4714-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1918215</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82452882</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1030,6 +1045,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82452884</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2211946</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,8 +1267,20 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4342009</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>